--- a/weekly_schedule_output.xlsx
+++ b/weekly_schedule_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21:30-23:59</t>
+          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
+          <t>04:30-09:30 [Breaks: 07:00]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -707,6 +707,48 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>05:00-09:00 [Breaks: 07:00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dhruv Patel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21:30-23:59</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Off</t>
         </is>
       </c>
     </row>

--- a/weekly_schedule_output.xlsx
+++ b/weekly_schedule_output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21:30-23:59</t>
+          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>04:30-11:31 [Breaks: 06:15, 08:00, 09:45]</t>
+          <t>04:30-08:30 [Breaks: 06:30]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21:30-23:59</t>
+          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
+          <t>04:30-12:00 [Breaks: 06:15, 08:15, 10:00]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>04:30-09:31 [Breaks: 07:00]</t>
+          <t>04:30-08:30 [Breaks: 06:30]</t>
         </is>
       </c>
     </row>
@@ -587,49 +587,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Dhruv Patel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>05:00-13:00 [Breaks: 07:00, 09:00, 11:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>04:30-09:30 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>James Abate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,56 +664,56 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12:00-20:00 [Breaks: 14:00, 16:00, 18:00]</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Bri Beauchamp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>05:00-13:00 [Breaks: 07:00, 09:00, 11:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>04:30-12:30 [Breaks: 06:30, 08:30, 10:30]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>04:30-08:30 [Breaks: 06:30]</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>05:00-09:00 [Breaks: 07:00]</t>
+          <t>Off</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dhruv Patel</t>
+          <t>Elisa Cooper</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -728,25 +728,655 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>15:30-21:30 [Breaks: 18:30]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15:30-21:30 [Breaks: 18:30]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Izzy Everitt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Courtney Gardner</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Charles High</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>21:30-23:59</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Melody Hollis</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15:00-21:30 [Breaks: 16:30, 18:15]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Emi Howard</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:30-21:30 [Breaks: 15:30, 17:30, 19:30]</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:30-21:30 [Breaks: 15:30, 17:30, 19:30]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13:30-21:30 [Breaks: 15:30, 17:30, 19:30]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>13:30-21:30 [Breaks: 15:30, 17:30, 19:30]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13:30-18:30 [Breaks: 16:00]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>13:30-17:30 [Breaks: 15:30]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taylor King</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Joie Mcghee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sophie Meeks</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16:00-00:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00-00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21:30-23:59</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16:00-00:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10:30-18:30 [Breaks: 12:30, 14:30, 16:30]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>10:30-18:30 [Breaks: 12:30, 14:30, 16:30]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abby Mullen</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Noelle Pereira</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Justin Pettit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Alex Polk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:00-21:30 [Breaks: 15:45, 17:45, 19:30]</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>14:00-21:30 [Breaks: 15:45, 17:45, 19:30]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kaden Shafer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Maksim Sostaric</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:30-00:30</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21:30-23:59</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10:00-18:00 [Breaks: 12:00, 14:00, 16:00]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kendra Soto</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Off</t>
         </is>
